--- a/services/worker/tests/fixtures/bootstrap_sample.xlsx
+++ b/services/worker/tests/fixtures/bootstrap_sample.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#lazarus #malware #appleseed #cve-2024-1234 #crypto</t>
+          <t>#lazarus #appleseed #cve-2024-1234 #crypto</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>#konni #malware #bluelight</t>
+          <t>#konni #bluelight</t>
         </is>
       </c>
     </row>
